--- a/thaco/API/1 MID Data- VPTQ.xlsx
+++ b/thaco/API/1 MID Data- VPTQ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/API/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DB519A-A0EF-C74F-BC10-CAC55B0460D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA5651F-EACD-EE4A-AE36-F0BC0B47515E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38400" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="761" xr2:uid="{D2D6ECD8-DC99-4D28-8DAC-0623419D46D2}"/>
   </bookViews>
@@ -2649,7 +2649,7 @@
     <definedName name="PRESS">#REF!</definedName>
     <definedName name="PRICE">#REF!</definedName>
     <definedName name="PRICE1">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Bảng lương tạm ứng kỳ 1'!$A$1:$AP$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Bảng lương tạm ứng kỳ 1'!$B$1:$AP$16</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="PRINT_AREA_MI1">#REF!</definedName>
@@ -4202,7 +4202,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
   <si>
     <t xml:space="preserve">Ngày công thực tế tháng </t>
   </si>
@@ -4246,9 +4246,6 @@
     <t>Thu nhập chịu thuế khác</t>
   </si>
   <si>
-    <t>Tham gia BHXH</t>
-  </si>
-  <si>
     <t>Quyết toán thuế</t>
   </si>
   <si>
@@ -4369,9 +4366,6 @@
     <t>LT</t>
   </si>
   <si>
-    <t>x</t>
-  </si>
-  <si>
     <t>Nguyễn Thành An</t>
   </si>
   <si>
@@ -4439,6 +4433,9 @@
   </si>
   <si>
     <t>ĐT PCCC</t>
+  </si>
+  <si>
+    <t>TT</t>
   </si>
 </sst>
 </file>
@@ -4866,7 +4863,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5003,6 +5000,135 @@
     <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="17" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="17" fillId="2" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="17" fillId="2" borderId="19" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="17" fillId="2" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5013,15 +5139,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5039,125 +5156,8 @@
     <xf numFmtId="165" fontId="6" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="17" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="17" fillId="2" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="17" fillId="2" borderId="19" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="17" fillId="2" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -5171,7 +5171,27 @@
     <cellStyle name="Per cent" xfId="2" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="8" xr:uid="{2763F245-BD58-41B8-A450-D1B9FA8F507A}"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5545,17 +5565,17 @@
   <dimension ref="A1:BA16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="8.5" style="36" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="37" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5" style="38" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="5.5" style="38" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="5.5" style="39" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="13.6640625" style="40" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5" style="50" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="21" width="7.1640625" style="41" customWidth="1"/>
-    <col min="22" max="29" width="12.33203125" style="40" customWidth="1"/>
-    <col min="30" max="30" width="13" style="40" customWidth="1"/>
-    <col min="31" max="31" width="6.6640625" style="40" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="43"/>
+    <col min="2" max="2" width="8.5" style="36" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5" style="38" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="5.5" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="5.5" style="39" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="13.6640625" style="40" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5" style="50" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="22" width="7.1640625" style="41" customWidth="1"/>
+    <col min="23" max="30" width="12.33203125" style="40" customWidth="1"/>
+    <col min="31" max="31" width="13" style="40" customWidth="1"/>
     <col min="32" max="42" width="10.5" style="40" customWidth="1"/>
     <col min="43" max="46" width="12.6640625" style="40" customWidth="1" outlineLevel="1"/>
     <col min="47" max="48" width="10.6640625" style="42" customWidth="1" outlineLevel="1"/>
@@ -5567,68 +5587,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" s="46" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="99" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="C1" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="102" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="65" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" s="68" t="s">
+      <c r="F1" s="105" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="H1" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="71" t="s">
+      <c r="I1" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="51"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="98"/>
+      <c r="T1" s="98"/>
+      <c r="U1" s="98"/>
+      <c r="V1" s="98"/>
       <c r="W1" s="51"/>
-      <c r="X1" s="68" t="s">
+      <c r="X1" s="51"/>
+      <c r="Y1" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" s="68" t="s">
+      <c r="Z1" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="Z1" s="68" t="s">
+      <c r="AA1" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="AA1" s="68" t="s">
+      <c r="AB1" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="AB1" s="68" t="s">
+      <c r="AC1" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="AC1" s="68" t="s">
+      <c r="AD1" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="AD1" s="59" t="s">
+      <c r="AE1" s="57" t="s">
         <v>13</v>
-      </c>
-      <c r="AE1" s="59" t="s">
-        <v>14</v>
       </c>
       <c r="AF1" s="52"/>
       <c r="AG1" s="52"/>
@@ -5639,182 +5659,182 @@
       <c r="AL1" s="52"/>
       <c r="AM1" s="52"/>
       <c r="AN1" s="53"/>
-      <c r="AO1" s="92" t="s">
+      <c r="AO1" s="82" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP1" s="83"/>
+      <c r="AQ1" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="AP1" s="93"/>
-      <c r="AQ1" s="94" t="s">
+      <c r="AR1" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="AR1" s="80" t="s">
+      <c r="AS1" s="68"/>
+      <c r="AT1" s="68"/>
+      <c r="AU1" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="86" t="s">
+      <c r="AV1" s="76" t="s">
         <v>18</v>
-      </c>
-      <c r="AV1" s="89" t="s">
-        <v>19</v>
       </c>
       <c r="AZ1" s="3"/>
       <c r="BA1" s="3"/>
     </row>
     <row r="2" spans="1:53" s="46" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="73" t="s">
+      <c r="A2" s="100"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="K2" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="73" t="s">
+      <c r="L2" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="73" t="s">
+      <c r="M2" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="73" t="s">
+      <c r="N2" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="73" t="s">
+      <c r="O2" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="73" t="s">
+      <c r="P2" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="73" t="s">
+      <c r="Q2" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="73" t="s">
+      <c r="R2" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="73" t="s">
+      <c r="S2" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="73" t="s">
+      <c r="T2" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="S2" s="76" t="s">
+      <c r="U2" s="91"/>
+      <c r="V2" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="T2" s="77"/>
-      <c r="U2" s="73" t="s">
+      <c r="W2" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="V2" s="99" t="s">
+      <c r="X2" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="W2" s="59" t="s">
-        <v>34</v>
-      </c>
-      <c r="X2" s="69"/>
-      <c r="Y2" s="69"/>
-      <c r="Z2" s="69"/>
-      <c r="AA2" s="69"/>
-      <c r="AB2" s="69"/>
-      <c r="AC2" s="69"/>
-      <c r="AD2" s="60"/>
-      <c r="AE2" s="60"/>
+      <c r="Y2" s="95"/>
+      <c r="Z2" s="95"/>
+      <c r="AA2" s="95"/>
+      <c r="AB2" s="95"/>
+      <c r="AC2" s="95"/>
+      <c r="AD2" s="95"/>
+      <c r="AE2" s="62"/>
       <c r="AF2" s="52"/>
       <c r="AG2" s="52"/>
       <c r="AH2" s="52"/>
-      <c r="AI2" s="104" t="s">
+      <c r="AI2" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="61"/>
+      <c r="AO2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="AJ2" s="105"/>
-      <c r="AK2" s="105"/>
-      <c r="AL2" s="105"/>
-      <c r="AM2" s="105"/>
-      <c r="AN2" s="106"/>
-      <c r="AO2" s="60" t="s">
+      <c r="AP2" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="AP2" s="60" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ2" s="95"/>
-      <c r="AR2" s="82"/>
-      <c r="AS2" s="83"/>
-      <c r="AT2" s="83"/>
-      <c r="AU2" s="87"/>
-      <c r="AV2" s="90"/>
+      <c r="AQ2" s="85"/>
+      <c r="AR2" s="69"/>
+      <c r="AS2" s="70"/>
+      <c r="AT2" s="70"/>
+      <c r="AU2" s="74"/>
+      <c r="AV2" s="77"/>
       <c r="AZ2" s="3"/>
       <c r="BA2" s="3"/>
     </row>
     <row r="3" spans="1:53" s="2" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="74"/>
-      <c r="P3" s="74"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="74"/>
-      <c r="S3" s="78"/>
-      <c r="T3" s="79"/>
-      <c r="U3" s="74"/>
-      <c r="V3" s="100"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="69"/>
-      <c r="Y3" s="69"/>
-      <c r="Z3" s="69"/>
-      <c r="AA3" s="69"/>
-      <c r="AB3" s="69"/>
-      <c r="AC3" s="69"/>
-      <c r="AD3" s="60"/>
-      <c r="AE3" s="60"/>
-      <c r="AF3" s="97" t="s">
+      <c r="A3" s="100"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="92"/>
+      <c r="U3" s="93"/>
+      <c r="V3" s="80"/>
+      <c r="W3" s="88"/>
+      <c r="X3" s="62"/>
+      <c r="Y3" s="95"/>
+      <c r="Z3" s="95"/>
+      <c r="AA3" s="95"/>
+      <c r="AB3" s="95"/>
+      <c r="AC3" s="95"/>
+      <c r="AD3" s="95"/>
+      <c r="AE3" s="62"/>
+      <c r="AF3" s="63" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG3" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="AG3" s="97" t="s">
+      <c r="AH3" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="AH3" s="97" t="s">
+      <c r="AI3" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="AI3" s="97" t="s">
+      <c r="AJ3" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="AJ3" s="102" t="s">
+      <c r="AK3" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="AK3" s="97" t="s">
+      <c r="AL3" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="AL3" s="102" t="s">
+      <c r="AM3" s="65" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN3" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="AM3" s="102" t="s">
-        <v>75</v>
-      </c>
-      <c r="AN3" s="59" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO3" s="60"/>
-      <c r="AP3" s="60"/>
-      <c r="AQ3" s="96"/>
-      <c r="AR3" s="84"/>
-      <c r="AS3" s="85"/>
-      <c r="AT3" s="85"/>
-      <c r="AU3" s="88"/>
-      <c r="AV3" s="91"/>
+      <c r="AO3" s="62"/>
+      <c r="AP3" s="62"/>
+      <c r="AQ3" s="86"/>
+      <c r="AR3" s="71"/>
+      <c r="AS3" s="72"/>
+      <c r="AT3" s="72"/>
+      <c r="AU3" s="75"/>
+      <c r="AV3" s="78"/>
       <c r="AW3" s="1" t="s">
         <v>0</v>
       </c>
@@ -5822,64 +5842,64 @@
       <c r="BA3" s="3"/>
     </row>
     <row r="4" spans="1:53" s="2" customFormat="1" ht="28">
-      <c r="A4" s="58"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="75"/>
-      <c r="M4" s="75"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="47" t="s">
+      <c r="A4" s="101"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
+      <c r="M4" s="81"/>
+      <c r="N4" s="81"/>
+      <c r="O4" s="81"/>
+      <c r="P4" s="81"/>
+      <c r="Q4" s="81"/>
+      <c r="R4" s="81"/>
+      <c r="S4" s="81"/>
+      <c r="T4" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="T4" s="47" t="s">
+      <c r="V4" s="81"/>
+      <c r="W4" s="89"/>
+      <c r="X4" s="58"/>
+      <c r="Y4" s="96"/>
+      <c r="Z4" s="96"/>
+      <c r="AA4" s="96"/>
+      <c r="AB4" s="96"/>
+      <c r="AC4" s="96"/>
+      <c r="AD4" s="96"/>
+      <c r="AE4" s="58"/>
+      <c r="AF4" s="64"/>
+      <c r="AG4" s="64"/>
+      <c r="AH4" s="64"/>
+      <c r="AI4" s="64"/>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="64"/>
+      <c r="AL4" s="66"/>
+      <c r="AM4" s="66"/>
+      <c r="AN4" s="58"/>
+      <c r="AO4" s="58"/>
+      <c r="AP4" s="58"/>
+      <c r="AQ4" s="86"/>
+      <c r="AR4" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="U4" s="75"/>
-      <c r="V4" s="101"/>
-      <c r="W4" s="61"/>
-      <c r="X4" s="70"/>
-      <c r="Y4" s="70"/>
-      <c r="Z4" s="70"/>
-      <c r="AA4" s="70"/>
-      <c r="AB4" s="70"/>
-      <c r="AC4" s="70"/>
-      <c r="AD4" s="61"/>
-      <c r="AE4" s="61"/>
-      <c r="AF4" s="98"/>
-      <c r="AG4" s="98"/>
-      <c r="AH4" s="98"/>
-      <c r="AI4" s="98"/>
-      <c r="AJ4" s="103"/>
-      <c r="AK4" s="98"/>
-      <c r="AL4" s="103"/>
-      <c r="AM4" s="103"/>
-      <c r="AN4" s="61"/>
-      <c r="AO4" s="61"/>
-      <c r="AP4" s="61"/>
-      <c r="AQ4" s="96"/>
-      <c r="AR4" s="48" t="s">
+      <c r="AS4" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="AS4" s="48" t="s">
+      <c r="AT4" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="AT4" s="48" t="s">
-        <v>50</v>
-      </c>
-      <c r="AU4" s="88"/>
-      <c r="AV4" s="91"/>
+      <c r="AU4" s="75"/>
+      <c r="AV4" s="78"/>
       <c r="AW4" s="45">
         <v>25</v>
       </c>
@@ -5888,48 +5908,48 @@
       <c r="BA4" s="3"/>
     </row>
     <row r="5" spans="1:53" s="8" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A5" s="54">
+      <c r="A5" s="8">
+        <v>1</v>
+      </c>
+      <c r="B5" s="54">
         <v>2405236</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="4">
+      <c r="F5" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="4">
         <v>9520000</v>
       </c>
-      <c r="G5" s="11">
+      <c r="H5" s="11">
         <v>1</v>
       </c>
-      <c r="H5" s="12">
+      <c r="I5" s="12">
         <v>11</v>
       </c>
-      <c r="I5" s="12"/>
       <c r="J5" s="12"/>
       <c r="K5" s="12"/>
-      <c r="L5" s="12">
+      <c r="L5" s="12"/>
+      <c r="M5" s="12">
         <v>2</v>
       </c>
-      <c r="M5" s="12"/>
       <c r="N5" s="12"/>
-      <c r="O5" s="12">
-        <v>0</v>
-      </c>
+      <c r="O5" s="12"/>
       <c r="P5" s="12">
         <v>0</v>
       </c>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12">
+      <c r="Q5" s="12">
         <v>0</v>
       </c>
+      <c r="R5" s="12"/>
       <c r="S5" s="12">
         <v>0</v>
       </c>
@@ -5939,7 +5959,9 @@
       <c r="U5" s="12">
         <v>0</v>
       </c>
-      <c r="V5" s="4"/>
+      <c r="V5" s="12">
+        <v>0</v>
+      </c>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
@@ -5948,9 +5970,7 @@
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
-      <c r="AE5" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="AE5" s="4"/>
       <c r="AF5" s="13"/>
       <c r="AG5" s="13"/>
       <c r="AH5" s="13">
@@ -5974,8 +5994,8 @@
       </c>
       <c r="AS5" s="7"/>
       <c r="AT5" s="7"/>
-      <c r="AU5" s="107" t="s">
-        <v>78</v>
+      <c r="AU5" s="56" t="s">
+        <v>76</v>
       </c>
       <c r="AV5" s="7"/>
       <c r="AW5" s="14"/>
@@ -5985,50 +6005,50 @@
       <c r="BA5" s="16"/>
     </row>
     <row r="6" spans="1:53" s="8" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A6" s="54">
+      <c r="A6" s="8">
+        <v>2</v>
+      </c>
+      <c r="B6" s="54">
         <v>2106723</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="C6" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="108" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="G6" s="4">
         <v>8480000</v>
       </c>
-      <c r="G6" s="11">
+      <c r="H6" s="11">
         <v>1</v>
       </c>
-      <c r="H6" s="12">
+      <c r="I6" s="12">
         <v>10.5</v>
       </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12">
+      <c r="J6" s="12"/>
+      <c r="K6" s="12">
         <v>0.5</v>
       </c>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12">
+      <c r="L6" s="12"/>
+      <c r="M6" s="12">
         <v>2</v>
       </c>
-      <c r="M6" s="12"/>
       <c r="N6" s="12"/>
-      <c r="O6" s="12">
-        <v>0</v>
-      </c>
+      <c r="O6" s="12"/>
       <c r="P6" s="12">
         <v>0</v>
       </c>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12">
+      <c r="Q6" s="12">
         <v>0</v>
       </c>
+      <c r="R6" s="12"/>
       <c r="S6" s="12">
         <v>0</v>
       </c>
@@ -6038,7 +6058,9 @@
       <c r="U6" s="12">
         <v>0</v>
       </c>
-      <c r="V6" s="4"/>
+      <c r="V6" s="12">
+        <v>0</v>
+      </c>
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
@@ -6047,9 +6069,7 @@
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
-      <c r="AE6" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="AE6" s="4"/>
       <c r="AF6" s="13"/>
       <c r="AG6" s="13"/>
       <c r="AH6" s="13"/>
@@ -6073,8 +6093,8 @@
         <v>0</v>
       </c>
       <c r="AT6" s="7"/>
-      <c r="AU6" s="107" t="s">
-        <v>77</v>
+      <c r="AU6" s="56" t="s">
+        <v>75</v>
       </c>
       <c r="AV6" s="7"/>
       <c r="AW6" s="14"/>
@@ -6084,48 +6104,48 @@
       <c r="BA6" s="16"/>
     </row>
     <row r="7" spans="1:53" s="8" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="8">
+        <v>3</v>
+      </c>
+      <c r="B7" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="10" t="s">
+      <c r="E7" s="108" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="G7" s="4">
         <v>7820000</v>
       </c>
-      <c r="G7" s="11">
+      <c r="H7" s="11">
         <v>1</v>
       </c>
-      <c r="H7" s="12">
+      <c r="I7" s="12">
         <v>11</v>
       </c>
-      <c r="I7" s="12"/>
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
-      <c r="L7" s="12">
+      <c r="L7" s="12"/>
+      <c r="M7" s="12">
         <v>2</v>
       </c>
-      <c r="M7" s="12"/>
       <c r="N7" s="12"/>
-      <c r="O7" s="12">
+      <c r="O7" s="12"/>
+      <c r="P7" s="12">
         <v>4</v>
       </c>
-      <c r="P7" s="12">
+      <c r="Q7" s="12">
         <v>0</v>
       </c>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12">
-        <v>0</v>
-      </c>
+      <c r="R7" s="12"/>
       <c r="S7" s="12">
         <v>0</v>
       </c>
@@ -6135,7 +6155,9 @@
       <c r="U7" s="12">
         <v>0</v>
       </c>
-      <c r="V7" s="4"/>
+      <c r="V7" s="12">
+        <v>0</v>
+      </c>
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
@@ -6144,9 +6166,7 @@
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
-      <c r="AE7" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="AE7" s="4"/>
       <c r="AF7" s="13"/>
       <c r="AG7" s="13"/>
       <c r="AH7" s="13"/>
@@ -6170,8 +6190,8 @@
         <v>0</v>
       </c>
       <c r="AT7" s="7"/>
-      <c r="AU7" s="107" t="s">
-        <v>71</v>
+      <c r="AU7" s="56" t="s">
+        <v>69</v>
       </c>
       <c r="AV7" s="7"/>
       <c r="AW7" s="14"/>
@@ -6181,50 +6201,50 @@
       <c r="BA7" s="16"/>
     </row>
     <row r="8" spans="1:53" s="8" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A8" s="54">
+      <c r="A8" s="8">
+        <v>4</v>
+      </c>
+      <c r="B8" s="54">
         <v>2406198</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="108" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="G8" s="4">
         <v>6990000</v>
       </c>
-      <c r="G8" s="11">
+      <c r="H8" s="11">
         <v>1</v>
       </c>
-      <c r="H8" s="12">
+      <c r="I8" s="12">
         <v>10.5</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12">
+      <c r="J8" s="12"/>
+      <c r="K8" s="12">
         <v>0.5</v>
       </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12">
+      <c r="L8" s="12"/>
+      <c r="M8" s="12">
         <v>2</v>
       </c>
-      <c r="M8" s="12"/>
       <c r="N8" s="12"/>
-      <c r="O8" s="12">
-        <v>0</v>
-      </c>
+      <c r="O8" s="12"/>
       <c r="P8" s="12">
         <v>0</v>
       </c>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12">
+      <c r="Q8" s="12">
         <v>0</v>
       </c>
+      <c r="R8" s="12"/>
       <c r="S8" s="12">
         <v>0</v>
       </c>
@@ -6234,7 +6254,9 @@
       <c r="U8" s="12">
         <v>0</v>
       </c>
-      <c r="V8" s="4"/>
+      <c r="V8" s="12">
+        <v>0</v>
+      </c>
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
@@ -6243,9 +6265,7 @@
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
-      <c r="AE8" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="AE8" s="4"/>
       <c r="AF8" s="13"/>
       <c r="AG8" s="13"/>
       <c r="AH8" s="13"/>
@@ -6269,8 +6289,8 @@
         <v>0</v>
       </c>
       <c r="AT8" s="7"/>
-      <c r="AU8" s="107" t="s">
-        <v>77</v>
+      <c r="AU8" s="56" t="s">
+        <v>75</v>
       </c>
       <c r="AV8" s="7"/>
       <c r="AW8" s="14"/>
@@ -6280,48 +6300,48 @@
       <c r="BA8" s="16"/>
     </row>
     <row r="9" spans="1:53" s="8" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="8">
+        <v>5</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="E9" s="108" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="G9" s="4">
         <v>4850000</v>
       </c>
-      <c r="G9" s="11">
+      <c r="H9" s="11">
         <v>1</v>
       </c>
-      <c r="H9" s="12">
+      <c r="I9" s="12">
         <v>11</v>
       </c>
-      <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
-      <c r="L9" s="12">
+      <c r="L9" s="12"/>
+      <c r="M9" s="12">
         <v>2</v>
       </c>
-      <c r="M9" s="12"/>
       <c r="N9" s="12"/>
-      <c r="O9" s="12">
+      <c r="O9" s="12"/>
+      <c r="P9" s="12">
         <v>4</v>
       </c>
-      <c r="P9" s="12">
+      <c r="Q9" s="12">
         <v>0</v>
       </c>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12">
-        <v>0</v>
-      </c>
+      <c r="R9" s="12"/>
       <c r="S9" s="12">
         <v>0</v>
       </c>
@@ -6331,7 +6351,9 @@
       <c r="U9" s="12">
         <v>0</v>
       </c>
-      <c r="V9" s="4"/>
+      <c r="V9" s="12">
+        <v>0</v>
+      </c>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
@@ -6340,9 +6362,7 @@
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
-      <c r="AE9" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="AE9" s="4"/>
       <c r="AF9" s="13"/>
       <c r="AG9" s="13"/>
       <c r="AH9" s="13"/>
@@ -6366,8 +6386,8 @@
         <v>0</v>
       </c>
       <c r="AT9" s="7"/>
-      <c r="AU9" s="107" t="s">
-        <v>71</v>
+      <c r="AU9" s="56" t="s">
+        <v>69</v>
       </c>
       <c r="AV9" s="7"/>
       <c r="AW9" s="14"/>
@@ -6377,50 +6397,50 @@
       <c r="BA9" s="16"/>
     </row>
     <row r="10" spans="1:53" s="8" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A10" s="54">
+      <c r="A10" s="8">
+        <v>6</v>
+      </c>
+      <c r="B10" s="54">
         <v>2406145</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="10" t="s">
+      <c r="C10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="108" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="4">
+      <c r="G10" s="4">
         <v>6340000</v>
       </c>
-      <c r="G10" s="11">
+      <c r="H10" s="11">
         <v>1</v>
       </c>
-      <c r="H10" s="12">
+      <c r="I10" s="12">
         <v>10.5</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12">
+      <c r="J10" s="12"/>
+      <c r="K10" s="12">
         <v>0.5</v>
       </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12">
+      <c r="L10" s="12"/>
+      <c r="M10" s="12">
         <v>2</v>
       </c>
-      <c r="M10" s="12"/>
       <c r="N10" s="12"/>
-      <c r="O10" s="12">
-        <v>0</v>
-      </c>
+      <c r="O10" s="12"/>
       <c r="P10" s="12">
         <v>0</v>
       </c>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12">
+      <c r="Q10" s="12">
         <v>0</v>
       </c>
+      <c r="R10" s="12"/>
       <c r="S10" s="12">
         <v>0</v>
       </c>
@@ -6430,7 +6450,9 @@
       <c r="U10" s="12">
         <v>0</v>
       </c>
-      <c r="V10" s="4"/>
+      <c r="V10" s="12">
+        <v>0</v>
+      </c>
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
@@ -6439,9 +6461,7 @@
       <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
       <c r="AD10" s="4"/>
-      <c r="AE10" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="AE10" s="4"/>
       <c r="AF10" s="13"/>
       <c r="AG10" s="13"/>
       <c r="AH10" s="13"/>
@@ -6465,8 +6485,8 @@
         <v>0</v>
       </c>
       <c r="AT10" s="7"/>
-      <c r="AU10" s="107" t="s">
-        <v>77</v>
+      <c r="AU10" s="56" t="s">
+        <v>75</v>
       </c>
       <c r="AV10" s="7"/>
       <c r="AW10" s="14"/>
@@ -6476,48 +6496,48 @@
       <c r="BA10" s="16"/>
     </row>
     <row r="11" spans="1:53" s="8" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="8">
+        <v>7</v>
+      </c>
+      <c r="B11" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="10" t="s">
+      <c r="E11" s="108" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="G11" s="4">
         <v>6340000</v>
       </c>
-      <c r="G11" s="11">
+      <c r="H11" s="11">
         <v>1</v>
       </c>
-      <c r="H11" s="12">
+      <c r="I11" s="12">
         <v>11</v>
       </c>
-      <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
-      <c r="L11" s="12">
+      <c r="L11" s="12"/>
+      <c r="M11" s="12">
         <v>2</v>
       </c>
-      <c r="M11" s="12"/>
       <c r="N11" s="12"/>
-      <c r="O11" s="12">
+      <c r="O11" s="12"/>
+      <c r="P11" s="12">
         <v>4</v>
       </c>
-      <c r="P11" s="12">
+      <c r="Q11" s="12">
         <v>0</v>
       </c>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12">
-        <v>0</v>
-      </c>
+      <c r="R11" s="12"/>
       <c r="S11" s="12">
         <v>0</v>
       </c>
@@ -6527,7 +6547,9 @@
       <c r="U11" s="12">
         <v>0</v>
       </c>
-      <c r="V11" s="4"/>
+      <c r="V11" s="12">
+        <v>0</v>
+      </c>
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
@@ -6536,9 +6558,7 @@
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
-      <c r="AE11" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="AE11" s="4"/>
       <c r="AF11" s="13"/>
       <c r="AG11" s="13"/>
       <c r="AH11" s="13"/>
@@ -6562,8 +6582,8 @@
         <v>0</v>
       </c>
       <c r="AT11" s="7"/>
-      <c r="AU11" s="107" t="s">
-        <v>71</v>
+      <c r="AU11" s="56" t="s">
+        <v>69</v>
       </c>
       <c r="AV11" s="7"/>
       <c r="AW11" s="14"/>
@@ -6573,9 +6593,8 @@
       <c r="BA11" s="16"/>
     </row>
     <row r="12" spans="1:53" s="18" customFormat="1" ht="19">
-      <c r="A12" s="17"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="20"/>
+      <c r="B12" s="17"/>
+      <c r="H12" s="19"/>
       <c r="I12" s="20"/>
       <c r="J12" s="20"/>
       <c r="K12" s="20"/>
@@ -6585,10 +6604,11 @@
       <c r="O12" s="20"/>
       <c r="P12" s="20"/>
       <c r="Q12" s="20"/>
-      <c r="R12" s="21"/>
+      <c r="R12" s="20"/>
       <c r="S12" s="21"/>
-      <c r="T12" s="22"/>
+      <c r="T12" s="21"/>
       <c r="U12" s="22"/>
+      <c r="V12" s="22"/>
       <c r="AL12" s="23"/>
       <c r="AM12" s="23"/>
       <c r="AN12" s="23"/>
@@ -6601,25 +6621,24 @@
       <c r="AX12" s="25"/>
     </row>
     <row r="13" spans="1:53" s="29" customFormat="1" ht="21" customHeight="1">
-      <c r="A13" s="26"/>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
       <c r="D13" s="26"/>
       <c r="E13" s="26"/>
       <c r="F13" s="26"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="28"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="27"/>
       <c r="I13" s="28"/>
       <c r="J13" s="28"/>
       <c r="K13" s="28"/>
       <c r="L13" s="28"/>
       <c r="M13" s="28"/>
       <c r="N13" s="28"/>
-      <c r="R13" s="30"/>
-      <c r="S13" s="28"/>
-      <c r="T13" s="26"/>
+      <c r="O13" s="28"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="28"/>
       <c r="U13" s="26"/>
-      <c r="X13" s="26"/>
+      <c r="V13" s="26"/>
       <c r="Y13" s="26"/>
       <c r="Z13" s="26"/>
       <c r="AA13" s="26"/>
@@ -6632,7 +6651,7 @@
       <c r="AJ13" s="26"/>
       <c r="AK13" s="26"/>
       <c r="AL13" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AM13" s="26"/>
       <c r="AN13" s="26"/>
@@ -6644,21 +6663,20 @@
       <c r="AT13" s="32"/>
     </row>
     <row r="14" spans="1:53" s="29" customFormat="1" ht="18" customHeight="1">
-      <c r="A14" s="33"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="30"/>
+      <c r="B14" s="33"/>
+      <c r="H14" s="27"/>
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
       <c r="K14" s="30"/>
       <c r="L14" s="30"/>
       <c r="M14" s="30"/>
       <c r="N14" s="30"/>
-      <c r="O14" s="28"/>
-      <c r="R14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="28"/>
       <c r="S14" s="30"/>
-      <c r="T14" s="34"/>
+      <c r="T14" s="30"/>
       <c r="U14" s="34"/>
-      <c r="AD14" s="26"/>
+      <c r="V14" s="34"/>
       <c r="AE14" s="26"/>
       <c r="AJ14" s="26"/>
       <c r="AK14" s="31"/>
@@ -6669,19 +6687,57 @@
       <c r="AX14" s="35"/>
     </row>
     <row r="15" spans="1:53" ht="15" customHeight="1">
-      <c r="U15" s="40"/>
+      <c r="V15" s="40"/>
       <c r="AT15" s="40" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AX15" s="44"/>
     </row>
     <row r="16" spans="1:53" ht="73.5" customHeight="1">
-      <c r="G16" s="41"/>
-      <c r="U16" s="40"/>
+      <c r="H16" s="41"/>
+      <c r="V16" s="40"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="48">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="C1:C4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="F1:F4"/>
+    <mergeCell ref="G1:G4"/>
+    <mergeCell ref="H1:H4"/>
+    <mergeCell ref="I1:V1"/>
+    <mergeCell ref="Y1:Y4"/>
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="AE1:AE4"/>
+    <mergeCell ref="P2:P4"/>
+    <mergeCell ref="Q2:Q4"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="T2:U3"/>
+    <mergeCell ref="V2:V4"/>
+    <mergeCell ref="Z1:Z4"/>
+    <mergeCell ref="AA1:AA4"/>
+    <mergeCell ref="AB1:AB4"/>
+    <mergeCell ref="AC1:AC4"/>
+    <mergeCell ref="AD1:AD4"/>
+    <mergeCell ref="AR1:AT3"/>
+    <mergeCell ref="AU1:AU4"/>
+    <mergeCell ref="AV1:AV4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="M2:M4"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="AQ1:AQ4"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="AG3:AG4"/>
+    <mergeCell ref="W2:W4"/>
+    <mergeCell ref="X2:X4"/>
     <mergeCell ref="AN3:AN4"/>
     <mergeCell ref="AI2:AN2"/>
     <mergeCell ref="AO2:AO4"/>
@@ -6692,53 +6748,19 @@
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="AR1:AT3"/>
-    <mergeCell ref="AU1:AU4"/>
-    <mergeCell ref="AV1:AV4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="M2:M4"/>
-    <mergeCell ref="AE1:AE4"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="AQ1:AQ4"/>
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="AG3:AG4"/>
-    <mergeCell ref="V2:V4"/>
-    <mergeCell ref="W2:W4"/>
-    <mergeCell ref="AD1:AD4"/>
-    <mergeCell ref="O2:O4"/>
-    <mergeCell ref="P2:P4"/>
-    <mergeCell ref="Q2:Q4"/>
-    <mergeCell ref="R2:R4"/>
-    <mergeCell ref="S2:T3"/>
-    <mergeCell ref="U2:U4"/>
-    <mergeCell ref="Y1:Y4"/>
-    <mergeCell ref="Z1:Z4"/>
-    <mergeCell ref="AA1:AA4"/>
-    <mergeCell ref="AB1:AB4"/>
-    <mergeCell ref="AC1:AC4"/>
-    <mergeCell ref="F1:F4"/>
-    <mergeCell ref="G1:G4"/>
-    <mergeCell ref="H1:U1"/>
-    <mergeCell ref="X1:X4"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="C1:C4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:A11">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  <conditionalFormatting sqref="B5:B11">
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:A1048576 A1:A4">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
+  <conditionalFormatting sqref="B12:B1048576 B1:B4">
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A4">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.21" bottom="0.17" header="0.196850393700787" footer="0.196850393700787"/>
